--- a/MU/Test upload format/Normal/2025 - 2026/CP2 25-26.xlsx
+++ b/MU/Test upload format/Normal/2025 - 2026/CP2 25-26.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>custid</t>
   </si>
@@ -74,70 +74,40 @@
     <t>pan</t>
   </si>
   <si>
-    <t>newQ2252601</t>
+    <t>taruncategoryearlier</t>
+  </si>
+  <si>
+    <t>accountsrepaidsatisfactorily</t>
+  </si>
+  <si>
+    <t>AnyLoansInNPASuitFiledSettledOTS</t>
+  </si>
+  <si>
+    <t>modifiedloancat</t>
+  </si>
+  <si>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>CR13Q1252603</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>1000</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>01-07-2025</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>29-07-2026</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>AQPPL3</t>
-  </si>
-  <si>
-    <t>newQ2252602</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>1000000</t>
-  </si>
-  <si>
-    <t>AQPPL2141K</t>
-  </si>
-  <si>
-    <t>newQ2252603</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>30000</t>
-  </si>
-  <si>
-    <t>newQ2252604</t>
-  </si>
-  <si>
-    <t>newQ2252605</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>19970</t>
-  </si>
-  <si>
-    <t>2000000</t>
-  </si>
-  <si>
-    <t>AQPPL4</t>
+    <t>01-04-2025</t>
+  </si>
+  <si>
+    <t>100001</t>
+  </si>
+  <si>
+    <t>K</t>
   </si>
 </sst>
 </file>
@@ -167,10 +137,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -511,7 +481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -531,6 +501,34 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,7 +656,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -670,34 +668,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -782,7 +780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -797,18 +795,17 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,7 +819,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1342,8 +1339,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="26.8571428571429" customWidth="1"/>
@@ -1353,6 +1350,7 @@
     <col min="7" max="7" width="20.2857142857143" customWidth="1"/>
     <col min="8" max="8" width="21.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="19.2857142857143" customWidth="1"/>
+    <col min="10" max="10" width="13.5714285714286" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="18.4285714285714" customWidth="1"/>
     <col min="13" max="13" width="14.5714285714286" customWidth="1"/>
@@ -1360,7 +1358,7 @@
     <col min="15" max="15" width="12.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1406,216 +1404,64 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:15">
-      <c r="A2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>19</v>
+    <row r="2" s="1" customFormat="1" spans="1:20">
+      <c r="A2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="1">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1">
-        <v>2</v>
-      </c>
-      <c r="L2" s="1">
+        <v>22</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="10">
         <v>1</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="L2" s="10">
+        <v>1</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="S2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="1">
-        <v>2</v>
-      </c>
-      <c r="K3" s="1">
-        <v>2</v>
-      </c>
-      <c r="L3" s="1">
-        <v>2</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="1">
-        <v>3</v>
-      </c>
-      <c r="L4" s="1">
-        <v>3</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
